--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/maule.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M159"/>
+  <dimension ref="A1:M160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>5243.19</v>
+        <v>5214.47</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3293.91</v>
+        <v>3305.66</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3293.91</v>
+        <v>3305.66</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2803.14</v>
+        <v>2812.36</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>9488.719999999999</v>
+        <v>9519.93</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1086.76</v>
+        <v>1105.52</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1174.47</v>
+        <v>1194.74</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6171.87</v>
+        <v>6200.61</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>7480.71</v>
+        <v>7534.64</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>6009.85</v>
+        <v>5985.08</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3950.09</v>
+        <v>3943.97</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>8624.780000000001</v>
+        <v>8669.33</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1412.86</v>
+        <v>1422.83</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>16110.67</v>
+        <v>15906.03</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>808.23</v>
+        <v>797.96</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1046.14</v>
+        <v>1035.73</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2330.19</v>
+        <v>2325.14</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>808.23</v>
+        <v>798.87</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>9494.879999999999</v>
+        <v>9414.450000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1543.97</v>
+        <v>1530.89</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1820.42</v>
+        <v>1818.95</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2900.67</v>
+        <v>2898.34</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>14684.66</v>
+        <v>14672.85</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>19035.66</v>
+        <v>19020.36</v>
       </c>
     </row>
     <row r="26">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>22389.57</v>
+        <v>22371.57</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2436-1568-CM25</t>
+          <t>707420-206-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>TECNOQUIM SPA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.378.846-6</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3131.74</v>
+        <v>1858.76</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>707420-206-CM25</t>
+          <t>2436-1565-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>TECNOQUIM SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>76.378.846-6</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1850.38</v>
+        <v>3379.38</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2436-1565-CM25</t>
+          <t>2436-1568-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3364.14</v>
+        <v>3145.93</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2763.72</v>
+        <v>2759.84</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3832.69</v>
+        <v>3827.31</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3539.68</v>
+        <v>3564.04</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>5170.22</v>
+        <v>5214.4</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>7856.74</v>
+        <v>7923.89</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1022.15</v>
+        <v>1033.11</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1476.58</v>
+        <v>1495.56</v>
       </c>
     </row>
     <row r="37">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2804.5</v>
+        <v>2819.83</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4451-13-CM26</t>
+          <t>4451-12-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.099.725-0</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2281.16</v>
+        <v>7783.24</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4451-12-CM26</t>
+          <t>4451-13-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.099.725-0</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>7969.67</v>
+        <v>2227.8</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>894.45</v>
+        <v>881.63</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>821.6</v>
+        <v>809.8200000000001</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>9685.459999999999</v>
+        <v>9545.889999999999</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>5917.37</v>
+        <v>5832.1</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>78843.28999999999</v>
+        <v>77824.28999999999</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>4224.8</v>
+        <v>4170.2</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1776.99</v>
+        <v>1779.46</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>3446.89</v>
+        <v>3451.68</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>17461.05</v>
+        <v>17485.29</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>8147.29</v>
+        <v>8141.73</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>4443.63</v>
+        <v>4420.15</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>3616.91</v>
+        <v>3640.61</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1281.04</v>
+        <v>1298.29</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>11004.46</v>
+        <v>11152.65</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>4153.97</v>
+        <v>4279.93</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1989.96</v>
+        <v>2049.1</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>877.5700000000001</v>
+        <v>880.11</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>9806.440000000001</v>
+        <v>9857.09</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2121.31</v>
+        <v>2112.37</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>4606.58</v>
+        <v>4619.23</v>
       </c>
     </row>
     <row r="60">
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>6110.58</v>
+        <v>6153.12</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4473-54-CM26</t>
+          <t>4451-98-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.100.200-4</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE ROMERAL</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>3951.9</v>
+        <v>1066.69</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4451-98-CM26</t>
+          <t>4473-54-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.100.200-4</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I.MUNICIPALIDAD DE ROMERAL</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1059.71</v>
+        <v>3977.92</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>13118.43</v>
+        <v>13235.27</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>812.89</v>
+        <v>811.6900000000001</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>10481.31</v>
+        <v>10424.23</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>5959.53</v>
+        <v>5923.31</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1677.91</v>
+        <v>1667.71</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1016.18</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>6121.55</v>
+        <v>6097.92</v>
       </c>
     </row>
     <row r="70">
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>9209.969999999999</v>
+        <v>9257.66</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4451-118-CM26</t>
+          <t>4473-81-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.100.200-4</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I.MUNICIPALIDAD DE ROMERAL</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>6814.59</v>
+        <v>7485.51</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>4473-81-CM26</t>
+          <t>4451-118-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.100.200-4</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE ROMERAL</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>7478.31</v>
+        <v>6821.16</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>13162.16</v>
+        <v>13379.09</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2811.07</v>
+        <v>2774.88</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1017.5</v>
+        <v>1035.95</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1472.72</v>
+        <v>1472.64</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>14242.44</v>
+        <v>14241.71</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>11864.9</v>
+        <v>11913.91</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>8004.8</v>
+        <v>7982.72</v>
       </c>
     </row>
     <row r="80">
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>934.45</v>
+        <v>923.67</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1208066-103-CM26</t>
+          <t>3399-54-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.946.800-7</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2309.1</v>
+        <v>11728.37</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3399-54-CM26</t>
+          <t>1208066-103-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5414,17 +5414,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.946.800-7</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>11905.95</v>
+        <v>2274.66</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>3365.27</v>
+        <v>3345.94</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1088.81</v>
+        <v>1084.12</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>871.36</v>
+        <v>867.61</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>23079.23</v>
+        <v>22979.8</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1981.05</v>
+        <v>1972.51</v>
       </c>
     </row>
     <row r="88">
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>8423.5</v>
+        <v>8387.209999999999</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3756-195-CM26</t>
+          <t>3756-193-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>5287.18</v>
+        <v>33312.38</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3756-193-CM26</t>
+          <t>3756-195-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>33801.39</v>
+        <v>5210.69</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>7851.71</v>
+        <v>7669.01</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>9622.110000000001</v>
+        <v>9432.35</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>8710.360000000001</v>
+        <v>8552.4</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>3187.86</v>
+        <v>3102.5</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2780.34</v>
+        <v>2803.93</v>
       </c>
     </row>
     <row r="96">
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>4272.12</v>
+        <v>4264.98</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2827-295-CM26</t>
+          <t>3756-255-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>69.120.100-7</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>2158.84</v>
+        <v>5287.86</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3756-255-CM26</t>
+          <t>2827-295-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>69.120.100-7</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>5223.57</v>
+        <v>2185.41</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2436-429-CM26</t>
+          <t>4473-140-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6451,17 +6451,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.100.200-4</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I.MUNICIPALIDAD DE ROMERAL</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>TECNOQUIM SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.378.846-6</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>814.4299999999999</v>
+        <v>1950.2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>4473-140-CM26</t>
+          <t>2436-429-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6512,17 +6512,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>69.100.200-4</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE ROMERAL</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>TECNOQUIM SPA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>76.378.846-6</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1924.58</v>
+        <v>825.27</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1199-91-CM26</t>
+          <t>1851-20-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6573,17 +6573,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>860.83</v>
+        <v>41745.06</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1851-20-CM26</t>
+          <t>1199-91-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6634,17 +6634,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>41207.32</v>
+        <v>872.0700000000001</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1112.03</v>
+        <v>1139.4</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>9345</v>
+        <v>9429.190000000001</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>37705.7</v>
+        <v>37946.86</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>987.11</v>
+        <v>990.22</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>4374.93</v>
+        <v>4393.06</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>3939.08</v>
+        <v>3955.41</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1778.06</v>
+        <v>1753.89</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>45510.18</v>
+        <v>45755.25</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>1755.98</v>
+        <v>1775.62</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>4175.6</v>
+        <v>4191.42</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>1720.1</v>
+        <v>1726.61</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>958.17</v>
+        <v>955.75</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>10738.45</v>
+        <v>10631.36</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>3095.51</v>
+        <v>3061.83</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>11639.37</v>
+        <v>11612.95</v>
       </c>
     </row>
     <row r="118">
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>4591.17</v>
+        <v>4579.83</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>4451-283-CM26</t>
+          <t>4451-282-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
+          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>78.456.070-8</t>
+          <t>76.950.108-8</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>916.53</v>
+        <v>8786.030000000001</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>4451-282-CM26</t>
+          <t>4451-283-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
+          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>76.950.108-8</t>
+          <t>78.456.070-8</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>8743.08</v>
+        <v>921.04</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1516.18</v>
+        <v>1521.21</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1582.6</v>
+        <v>1587.63</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>1667.56</v>
+        <v>1691.42</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>965</v>
+        <v>978.8099999999999</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>2022.06</v>
+        <v>2045.78</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>1452.14</v>
+        <v>1476.7</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>3003.53</v>
+        <v>3034.07</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>1011.03</v>
+        <v>1003.36</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>2696.08</v>
+        <v>2650.53</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>9877.41</v>
+        <v>9737.23</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1757.81</v>
+        <v>1733.66</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>11623.4</v>
+        <v>11551.34</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>1801.37</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1371.65</v>
+        <v>1402.59</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>3042.89</v>
+        <v>3063.9</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2207.23</v>
+        <v>2214.06</v>
       </c>
     </row>
     <row r="137">
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>5136.86</v>
+        <v>5036.31</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>3385-154-CM26</t>
+          <t>3756-443-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -8865,13 +8865,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>18596.74</v>
+        <v>2046.42</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>3756-443-CM26</t>
+          <t>3385-154-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>2077.2</v>
+        <v>18321.21</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>13040.96</v>
+        <v>12772.95</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1588.43</v>
+        <v>1596.52</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>6540.48</v>
+        <v>6565.94</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>10353.97</v>
+        <v>10394.28</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>25651.62</v>
+        <v>25521.67</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2530.91</v>
+        <v>2536.3</v>
       </c>
     </row>
     <row r="146">
@@ -9353,13 +9353,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>16597.85</v>
+        <v>16633.22</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>3469-299-CM26</t>
+          <t>4085-447-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9379,17 +9379,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>69.120.300-k</t>
+          <t>69.130.600-3</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANCO</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9399,12 +9399,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>78.456.070-8</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1033.75</v>
+        <v>1716.37</v>
       </c>
     </row>
     <row r="148">
@@ -9475,13 +9475,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>6847.7</v>
+        <v>6892.34</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>4085-447-CM26</t>
+          <t>3469-299-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9501,17 +9501,17 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>69.130.600-3</t>
+          <t>69.120.300-k</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONGAVI</t>
+          <t>I MUNICIPALIDAD DE CHANCO</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>78.456.070-8</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1705.26</v>
+        <v>1040.49</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>3311-106-CM26</t>
+          <t>2291-1220-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9567,12 +9567,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9582,12 +9582,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.099.725-0</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9597,13 +9597,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2617.19</v>
+        <v>14819.6</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2291-1220-CM26</t>
+          <t>3311-106-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>76.099.725-0</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>14721.07</v>
+        <v>2634.71</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>27243.89</v>
+        <v>27157.83</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>11120.66</v>
+        <v>11085.53</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>21096.02</v>
+        <v>21029.38</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1513.43</v>
+        <v>1510.14</v>
       </c>
     </row>
     <row r="156">
@@ -9963,13 +9963,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1615.19</v>
+        <v>1611.68</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>4404-165-CM26</t>
+          <t>3385-178-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9989,17 +9989,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10024,13 +10024,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>11003.3</v>
+        <v>8455.41</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>3385-178-CM26</t>
+          <t>4404-165-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10050,17 +10050,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>10826.88</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,68 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>4575.16</v>
+        <v>4521.92</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>4451-499-CM26</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>69.110.500-8</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA WAY SPA</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>76.532.399-1</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="n">
+        <v>7664.54</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/maule.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/maule.xlsx
@@ -623,7 +623,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +871,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1302,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1367,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1615,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1802,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1928,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2054,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2241,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2672,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2737,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +2985,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3172,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3420,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3546,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4099,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4225,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4534,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4660,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4786,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5217,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5587,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5713,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +5961,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6148,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6213,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6522,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +6831,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7079,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7144,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7392,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7457,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7583,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +7831,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +7896,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8083,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8148,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8213,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8278,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8343,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8591,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +8961,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9026,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9213,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9339,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9648,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +9774,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10144,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10453,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +10701,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +10766,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +10831,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11201,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11327,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11636,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +11762,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +11949,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12136,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12201,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12449,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +12514,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +12762,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +12827,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +12892,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13018,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13266,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13331,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13396,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13461,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13526,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13591,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +13656,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +13721,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +13786,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +13851,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +13916,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +13981,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14046,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14111,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14176,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14241,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14306,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +14676,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +14863,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +14928,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +14993,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15058,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +15550,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +15676,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +15802,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +15989,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16298,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +16424,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +16489,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +16737,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +16802,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +16867,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +16932,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17119,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17306,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +17493,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +17558,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +17745,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +17993,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18058,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18123,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18188,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18436,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +18501,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +18749,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19119,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +19733,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +19920,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +19985,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20111,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20176,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20302,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +20367,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +20554,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +20619,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +20684,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +20810,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +20875,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +20940,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +21005,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20570,7 +21070,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +21196,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +21627,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +21753,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +21818,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +21883,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +21948,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22074,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +22200,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21729,7 +22265,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +22330,11 @@
           <t>76.156.939-2</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +22517,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +22582,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +22647,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22278,7 +22834,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +22899,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22400,7 +22964,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23090,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22583,7 +23155,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +23342,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +23529,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23132,7 +23716,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23193,7 +23781,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +24151,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23742,7 +24338,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/maule.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/maule.xlsx
@@ -3794,7 +3794,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6770,7 +6774,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24090,7 +24098,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/maule.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M383"/>
+  <dimension ref="A1:M401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1384,7 +1384,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4404-19-CM25</t>
+          <t>1199-21-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1404,17 +1404,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1439,13 +1439,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3954.46</v>
+        <v>1517.59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1199-21-CM25</t>
+          <t>4404-19-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1465,17 +1465,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1517.59</v>
+        <v>3954.46</v>
       </c>
     </row>
     <row r="18">
@@ -1567,7 +1567,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3505-42-CM25</t>
+          <t>1738-70-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1587,17 +1587,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.110.800-7</t>
+          <t>69.130.200-8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCAHUE</t>
+          <t>I MUNICIPALIDAD DE VILLA ALEGRE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1607,32 +1607,28 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOCIEDAD DE INVERSIONES MILCON SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>77.176.547-5</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3975.34</v>
+        <v>8083.91</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3505-41-CM25</t>
+          <t>2293-8-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1652,17 +1648,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.110.800-7</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCAHUE</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1672,12 +1668,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>14.205.876-6</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1687,13 +1683,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4272.59</v>
+        <v>900.47</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1738-70-CM25</t>
+          <t>3505-43-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1713,17 +1709,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.130.200-8</t>
+          <t>69.110.800-7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLA ALEGRE</t>
+          <t>I MUNICIPALIDAD DE PENCAHUE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1733,28 +1729,32 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES MILCON SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.176.547-5</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>8083.91</v>
+        <v>1951.44</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3505-43-CM25</t>
+          <t>3505-42-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1813,13 +1813,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1951.44</v>
+        <v>3975.34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2293-8-CM25</t>
+          <t>3505-41-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1839,17 +1839,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.110.800-7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE PENCAHUE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1859,12 +1859,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>14.205.876-6</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1874,13 +1874,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>900.47</v>
+        <v>4272.59</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4451-78-CM25</t>
+          <t>4451-79-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1920,32 +1920,28 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA WAY SPA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.532.399-1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>7402.94</v>
+        <v>20775.64</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4451-79-CM25</t>
+          <t>4134-124-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1970,12 +1966,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1985,12 +1981,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -2000,7 +1996,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>20775.64</v>
+        <v>1747.71</v>
       </c>
     </row>
     <row r="26">
@@ -2071,7 +2067,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4134-124-CM25</t>
+          <t>4451-78-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2096,12 +2092,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2111,22 +2107,26 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA WAY SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>76.532.399-1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1747.71</v>
+        <v>7402.94</v>
       </c>
     </row>
     <row r="28">
@@ -2319,7 +2319,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4451-114-CM25</t>
+          <t>4451-115-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
+          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>78.456.070-8</t>
+          <t>76.099.725-0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2374,13 +2374,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1459.33</v>
+        <v>869.63</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4451-115-CM25</t>
+          <t>4451-116-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.099.725-0</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2435,13 +2435,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>869.63</v>
+        <v>2391.1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4451-116-CM25</t>
+          <t>4451-114-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>78.456.070-8</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2391.1</v>
+        <v>1459.33</v>
       </c>
     </row>
     <row r="34">
@@ -2563,7 +2563,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2827-221-CM25</t>
+          <t>4404-39-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2583,17 +2583,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.120.100-7</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2603,28 +2603,32 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>DIMACO CONSTITUCION LTDA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>85.067.500-7</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1498.59</v>
+        <v>4928.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2436-335-CM25</t>
+          <t>2827-221-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2644,17 +2648,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.120.100-7</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2664,32 +2668,28 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>TECNOQUIM SPA</t>
+          <t>DIMACO CONSTITUCION LTDA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.378.846-6</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>85.067.500-7</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>3266.26</v>
+        <v>1498.59</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4404-39-CM25</t>
+          <t>2436-335-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>TECNOQUIM SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.378.846-6</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2748,7 +2748,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>4928.4</v>
+        <v>3266.26</v>
       </c>
     </row>
     <row r="38">
@@ -3250,7 +3250,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4451-183-CM25</t>
+          <t>3206-88-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.264.500-6</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>MAR DEL SUR SPA</t>
+          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>83.610.800-0</t>
+          <t>76.099.725-0</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3305,13 +3305,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>3318.96</v>
+        <v>1956.59</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3206-88-CM25</t>
+          <t>4451-183-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.264.500-6</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
+          <t>MAR DEL SUR SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.099.725-0</t>
+          <t>83.610.800-0</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3366,13 +3366,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1956.59</v>
+        <v>3318.96</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4168-623-CM25</t>
+          <t>1469-494-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3392,17 +3392,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.130.500-7</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3412,32 +3412,28 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>13010.82</v>
+        <v>2488.53</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1469-494-CM25</t>
+          <t>4168-623-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3457,17 +3453,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.130.500-7</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3477,28 +3473,32 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2488.53</v>
+        <v>13010.82</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2319-29-CM25</t>
+          <t>3385-49-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3523,12 +3523,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.130.100-1</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3538,32 +3538,28 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.456.070-8</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>138942.95</v>
+        <v>2638.41</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3385-49-CM25</t>
+          <t>2319-29-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3588,12 +3584,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>69.130.100-1</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3603,22 +3599,26 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>78.456.070-8</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2638.41</v>
+        <v>138942.95</v>
       </c>
     </row>
     <row r="52">
@@ -4307,7 +4307,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2291-558-CM25</t>
+          <t>1029-35-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4327,17 +4327,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4347,12 +4347,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
+          <t>INGENIERIA Y SEGURIDAD INDUSTRIAL KS LIMITADA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.099.725-0</t>
+          <t>76.488.070-6</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4362,13 +4362,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2011.98</v>
+        <v>24123.04</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1029-35-CM25</t>
+          <t>2291-557-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4388,17 +4388,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>INGENIERIA Y SEGURIDAD INDUSTRIAL KS LIMITADA</t>
+          <t>FERRETERIA LAS RASTRAS SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.488.070-6</t>
+          <t>76.851.313-9</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4423,13 +4423,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>24123.04</v>
+        <v>1097.52</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2291-557-CM25</t>
+          <t>2291-558-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>FERRETERIA LAS RASTRAS SPA</t>
+          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.851.313-9</t>
+          <t>76.099.725-0</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4484,13 +4484,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1097.52</v>
+        <v>2011.98</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3756-241-CM25</t>
+          <t>1199-107-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4530,32 +4530,28 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.967.556-6</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>20611.24</v>
+        <v>3273.61</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1199-107-CM25</t>
+          <t>1199-127-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4595,28 +4591,32 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.967.556-6</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
+          <t>77.745.829-9</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>3273.61</v>
+        <v>16008.88</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1199-127-CM25</t>
+          <t>3756-241-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4656,17 +4656,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4675,13 +4675,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>16008.88</v>
+        <v>20611.24</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4159-169-CM25</t>
+          <t>2436-543-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4701,17 +4701,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.130.700-K</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4721,28 +4721,32 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>COMERCIAL COMPARO LIMITADA</t>
+          <t>TECNOQUIM SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.290.943-K</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
+          <t>76.378.846-6</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>22857.43</v>
+        <v>1634.83</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2436-543-CM25</t>
+          <t>4159-169-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4762,17 +4766,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.130.700-K</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4782,26 +4786,22 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>TECNOQUIM SPA</t>
+          <t>COMERCIAL COMPARO LIMITADA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.378.846-6</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.290.943-K</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1634.83</v>
+        <v>22857.43</v>
       </c>
     </row>
     <row r="71">
@@ -4868,7 +4868,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2595-205-CM25</t>
+          <t>2291-618-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.130.700-K</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Francisco javier</t>
+          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.882.403-7</t>
+          <t>78.456.070-8</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4923,13 +4923,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1608.41</v>
+        <v>1721.61</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2291-618-CM25</t>
+          <t>2595-205-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.130.700-K</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>78.456.070-8</t>
+          <t>76.882.403-7</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4984,13 +4984,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1721.61</v>
+        <v>1608.41</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2595-206-CM25</t>
+          <t>2595-226-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5045,13 +5045,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>985.64</v>
+        <v>3186.54</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2595-226-CM25</t>
+          <t>2595-206-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>3186.54</v>
+        <v>985.64</v>
       </c>
     </row>
     <row r="76">
@@ -5608,7 +5608,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3767-82-CM25</t>
+          <t>1199-156-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5648,28 +5648,32 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>MAR DEL SUR SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>83.610.800-0</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
+          <t>77.745.829-9</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>6728.69</v>
+        <v>2766.4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1199-156-CM25</t>
+          <t>3767-82-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5694,12 +5698,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5709,26 +5713,22 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>MAR DEL SUR SPA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>83.610.800-0</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2766.4</v>
+        <v>6728.69</v>
       </c>
     </row>
     <row r="86">
@@ -6604,7 +6604,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1079566-177-CM25</t>
+          <t>872535-119-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6629,12 +6629,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.979.370-6</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6644,22 +6644,26 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>76.967.556-6</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>6855.6</v>
+        <v>1674.65</v>
       </c>
     </row>
     <row r="101">
@@ -6726,7 +6730,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>872535-119-CM25</t>
+          <t>872535-113-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6766,17 +6770,17 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6785,13 +6789,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1674.65</v>
+        <v>10454.1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>872535-113-CM25</t>
+          <t>1079566-177-CM25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6816,12 +6820,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>61.979.370-6</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6831,26 +6835,22 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.967.556-6</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>10454.1</v>
+        <v>6855.6</v>
       </c>
     </row>
     <row r="104">
@@ -7352,7 +7352,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>5053-3667-CM25</t>
+          <t>1199-192-CM25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -7411,13 +7411,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>744.4</v>
+        <v>8899.389999999999</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1199-192-CM25</t>
+          <t>5053-3667-CM25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7442,12 +7442,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7476,7 +7476,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>8899.389999999999</v>
+        <v>744.4</v>
       </c>
     </row>
     <row r="114">
@@ -9051,7 +9051,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>4134-567-CM25</t>
+          <t>2445-3320-CM25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9076,12 +9076,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9091,28 +9091,32 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>14.205.876-6</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>840.78</v>
+        <v>1484.9</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2445-3319-CM25</t>
+          <t>4134-567-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9137,12 +9141,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9152,12 +9156,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Importadora y Comercializadora Proinmin SpA</t>
+          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>76.949.422-7</t>
+          <t>14.205.876-6</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -9167,13 +9171,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1596.19</v>
+        <v>840.78</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2445-3320-CM25</t>
+          <t>2445-3319-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9213,26 +9217,22 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>Importadora y Comercializadora Proinmin SpA</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.949.422-7</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1484.9</v>
+        <v>1596.19</v>
       </c>
     </row>
     <row r="142">
@@ -9734,7 +9734,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>4089-549-CM25</t>
+          <t>4451-550-CM25</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9759,12 +9759,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>69.130.602-k</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONGAVI</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9774,32 +9774,28 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2364.39</v>
+        <v>2392.09</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>4451-550-CM25</t>
+          <t>4089-549-CM25</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9824,12 +9820,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.130.602-k</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9839,28 +9835,32 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>2392.09</v>
+        <v>2364.39</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1291-50-CM25</t>
+          <t>967-45-CM25</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9885,12 +9885,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
+          <t>Treck S.A.</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>78.456.070-8</t>
+          <t>96.542.490-3</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9915,13 +9915,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>859.86</v>
+        <v>3964.27</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>967-45-CM25</t>
+          <t>1291-50-CM25</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9946,12 +9946,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Treck S.A.</t>
+          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>96.542.490-3</t>
+          <t>78.456.070-8</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9976,7 +9976,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>3964.27</v>
+        <v>859.86</v>
       </c>
     </row>
     <row r="154">
@@ -10230,7 +10230,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1199-279-CM25</t>
+          <t>1208066-308-CM25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10250,17 +10250,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
+          <t>ELECTROCOM S A</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>78.456.070-8</t>
+          <t>96.355.000-6</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10285,13 +10285,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>731.7</v>
+        <v>4834.06</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1208066-308-CM25</t>
+          <t>1199-279-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10311,17 +10311,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10331,12 +10331,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>ELECTROCOM S A</t>
+          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>96.355.000-6</t>
+          <t>78.456.070-8</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10346,7 +10346,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>4834.06</v>
+        <v>731.7</v>
       </c>
     </row>
     <row r="160">
@@ -10413,7 +10413,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>4404-286-CM25</t>
+          <t>4404-293-CM25</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10453,32 +10453,28 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>COMERCIAL TRANCURA SPA</t>
+          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>77.823.479-3</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>78.456.070-8</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>1340.58</v>
+        <v>2574.25</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>4404-293-CM25</t>
+          <t>4404-286-CM25</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10518,22 +10514,26 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
+          <t>COMERCIAL TRANCURA SPA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>78.456.070-8</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr"/>
+          <t>77.823.479-3</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>2574.25</v>
+        <v>1340.58</v>
       </c>
     </row>
     <row r="163">
@@ -11352,7 +11352,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>3385-222-CM25</t>
+          <t>3385-223-CM25</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11407,13 +11407,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>7863.38</v>
+        <v>887.79</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>3385-223-CM25</t>
+          <t>3385-222-CM25</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11468,7 +11468,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>887.79</v>
+        <v>7863.38</v>
       </c>
     </row>
     <row r="178">
@@ -11596,7 +11596,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1469-3256-CM25</t>
+          <t>3385-227-CM25</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11616,17 +11616,17 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11636,17 +11636,17 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -11655,13 +11655,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>2820.81</v>
+        <v>17340.55</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1469-3257-CM25</t>
+          <t>1469-3256-CM25</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11701,28 +11701,32 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>FERRETERIA LAS RASTRAS SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>76.851.313-9</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>953.42</v>
+        <v>2820.81</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>3385-227-CM25</t>
+          <t>1469-3257-CM25</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11742,17 +11746,17 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11762,26 +11766,22 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>FERRETERIA LAS RASTRAS SPA</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.851.313-9</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>17340.55</v>
+        <v>953.42</v>
       </c>
     </row>
     <row r="183">
@@ -12348,7 +12348,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>3385-244-CM25</t>
+          <t>3385-243-CM25</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12388,28 +12388,32 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>78.456.070-8</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>1194.74</v>
+        <v>1105.52</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>3385-243-CM25</t>
+          <t>3385-244-CM25</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12449,26 +12453,22 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.456.070-8</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1105.52</v>
+        <v>1194.74</v>
       </c>
     </row>
     <row r="194">
@@ -13165,7 +13165,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>707420-189-CM25</t>
+          <t>1421-684-CM25</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13190,12 +13190,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13205,28 +13205,32 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>FERRETERIA LAS RASTRAS SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>76.851.313-9</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1530.89</v>
+        <v>9414.450000000001</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1421-684-CM25</t>
+          <t>707420-189-CM25</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13251,12 +13255,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13266,32 +13270,28 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>FERRETERIA LAS RASTRAS SPA</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.851.313-9</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>9414.450000000001</v>
+        <v>1530.89</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1079566-641-CM25</t>
+          <t>1421-688-CM25</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>61.979.370-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13350,13 +13350,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>22371.57</v>
+        <v>1818.95</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1079566-640-CM25</t>
+          <t>1079566-637-CM25</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13415,13 +13415,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>19020.36</v>
+        <v>2898.34</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1421-688-CM25</t>
+          <t>1079566-639-CM25</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13446,12 +13446,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.979.370-6</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13480,13 +13480,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>1818.95</v>
+        <v>14672.85</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1079566-637-CM25</t>
+          <t>1079566-640-CM25</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13545,13 +13545,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>2898.34</v>
+        <v>19020.36</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1079566-639-CM25</t>
+          <t>1079566-641-CM25</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13610,13 +13610,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>14672.85</v>
+        <v>22371.57</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>707420-206-CM25</t>
+          <t>2436-1568-CM25</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13641,12 +13641,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13656,12 +13656,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>TECNOQUIM SPA</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>76.378.846-6</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1858.76</v>
+        <v>3145.93</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2436-1565-CM25</t>
+          <t>707420-206-CM25</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13706,12 +13706,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13721,12 +13721,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>TECNOQUIM SPA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>76.378.846-6</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -13740,13 +13740,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>3379.38</v>
+        <v>1858.76</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2436-1568-CM25</t>
+          <t>2436-1565-CM25</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13805,7 +13805,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>3145.93</v>
+        <v>3379.38</v>
       </c>
     </row>
     <row r="215">
@@ -14701,7 +14701,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1079566-14-CM26</t>
+          <t>1079566-13-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14756,13 +14756,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>4170.2</v>
+        <v>77824.28999999999</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1079566-13-CM26</t>
+          <t>1079566-14-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14817,13 +14817,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>77824.28999999999</v>
+        <v>4170.2</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2436-27-CM26</t>
+          <t>2436-29-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14882,13 +14882,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>1779.46</v>
+        <v>17485.29</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2436-28-CM26</t>
+          <t>2436-27-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14947,13 +14947,13 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>3451.68</v>
+        <v>1779.46</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2436-29-CM26</t>
+          <t>2436-28-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -15012,7 +15012,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>17485.29</v>
+        <v>3451.68</v>
       </c>
     </row>
     <row r="234">
@@ -16697,7 +16697,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>3385-44-CM26</t>
+          <t>4168-348-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16722,12 +16722,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>69.130.500-7</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16737,17 +16737,17 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>BROKER SPA</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.819.582-8</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -16756,13 +16756,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>1472.64</v>
+        <v>14241.71</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>4168-348-CM26</t>
+          <t>3385-44-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16787,12 +16787,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>69.130.500-7</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -16802,17 +16802,17 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>BROKER SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>77.819.582-8</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -16821,7 +16821,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>14241.71</v>
+        <v>1472.64</v>
       </c>
     </row>
     <row r="263">
@@ -17018,7 +17018,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1208066-103-CM26</t>
+          <t>3399-54-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -17038,17 +17038,17 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.946.800-7</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -17058,28 +17058,32 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
-        </is>
-      </c>
-      <c r="K266" t="inlineStr"/>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>2274.66</v>
+        <v>11728.37</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>3399-54-CM26</t>
+          <t>1208066-103-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17099,17 +17103,17 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>61.946.800-7</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17119,26 +17123,22 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>11728.37</v>
+        <v>2274.66</v>
       </c>
     </row>
     <row r="268">
@@ -17205,7 +17205,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>3385-57-CM26</t>
+          <t>3756-192-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17230,12 +17230,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -17245,12 +17245,12 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
+          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>76.099.725-0</t>
+          <t>14.205.876-6</t>
         </is>
       </c>
       <c r="K269" t="inlineStr"/>
@@ -17260,7 +17260,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>867.61</v>
+        <v>8387.209999999999</v>
       </c>
     </row>
     <row r="270">
@@ -17331,7 +17331,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1426095-59-CM26</t>
+          <t>3385-57-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -17351,17 +17351,17 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -17371,12 +17371,12 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
+          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>78.456.070-8</t>
+          <t>76.099.725-0</t>
         </is>
       </c>
       <c r="K271" t="inlineStr"/>
@@ -17386,13 +17386,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>1972.51</v>
+        <v>867.61</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>3756-192-CM26</t>
+          <t>1426095-59-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17412,17 +17412,17 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17432,12 +17432,12 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
+          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>14.205.876-6</t>
+          <t>78.456.070-8</t>
         </is>
       </c>
       <c r="K272" t="inlineStr"/>
@@ -17447,13 +17447,13 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>8387.209999999999</v>
+        <v>1972.51</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>3756-193-CM26</t>
+          <t>3756-195-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17512,13 +17512,13 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>33312.38</v>
+        <v>5210.69</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>3756-195-CM26</t>
+          <t>3756-193-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17577,7 +17577,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>5210.69</v>
+        <v>33312.38</v>
       </c>
     </row>
     <row r="275">
@@ -18083,7 +18083,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>4473-140-CM26</t>
+          <t>2436-429-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18103,17 +18103,17 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>69.100.200-4</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE ROMERAL</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -18123,12 +18123,12 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>TECNOQUIM SPA</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>76.378.846-6</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -18142,13 +18142,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>1950.2</v>
+        <v>825.27</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2436-429-CM26</t>
+          <t>4473-140-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18168,17 +18168,17 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.100.200-4</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I.MUNICIPALIDAD DE ROMERAL</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18188,12 +18188,12 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>TECNOQUIM SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>76.378.846-6</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -18207,7 +18207,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>825.27</v>
+        <v>1950.2</v>
       </c>
     </row>
     <row r="285">
@@ -18896,7 +18896,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>848-85-CM26</t>
+          <t>3206-178-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -18921,12 +18921,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.264.500-6</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -18936,12 +18936,12 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>INGENIERIA Y SEGURIDAD INDUSTRIAL KS LIMITADA</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>76.488.070-6</t>
         </is>
       </c>
       <c r="K296" t="inlineStr"/>
@@ -18951,13 +18951,13 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>4191.42</v>
+        <v>1726.61</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>3206-178-CM26</t>
+          <t>848-85-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -18982,12 +18982,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>69.264.500-6</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -18997,12 +18997,12 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>INGENIERIA Y SEGURIDAD INDUSTRIAL KS LIMITADA</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>76.488.070-6</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K297" t="inlineStr"/>
@@ -19012,7 +19012,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>1726.61</v>
+        <v>4191.42</v>
       </c>
     </row>
     <row r="298">
@@ -20514,7 +20514,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>3385-154-CM26</t>
+          <t>3756-443-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -20534,17 +20534,17 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -20554,17 +20554,17 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -20573,13 +20573,13 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>18321.21</v>
+        <v>2046.42</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>3756-443-CM26</t>
+          <t>3385-154-CM26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -20599,17 +20599,17 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -20619,17 +20619,17 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -20638,7 +20638,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>2046.42</v>
+        <v>18321.21</v>
       </c>
     </row>
     <row r="324">
@@ -21465,7 +21465,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2291-1232-CM26</t>
+          <t>872535-187-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -21490,12 +21490,12 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -21505,12 +21505,12 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
+          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>76.099.725-0</t>
+          <t>78.456.070-8</t>
         </is>
       </c>
       <c r="K337" t="inlineStr"/>
@@ -21520,13 +21520,13 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>21029.38</v>
+        <v>27157.83</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>872535-187-CM26</t>
+          <t>2291-1232-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -21551,12 +21551,12 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -21566,12 +21566,12 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
+          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>78.456.070-8</t>
+          <t>76.099.725-0</t>
         </is>
       </c>
       <c r="K338" t="inlineStr"/>
@@ -21581,13 +21581,13 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>27157.83</v>
+        <v>21029.38</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>4452-534-CM26</t>
+          <t>3311-115-CM26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -21612,12 +21612,12 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -21627,32 +21627,28 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>BROKER SPA</t>
+          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>77.819.582-8</t>
-        </is>
-      </c>
-      <c r="K339" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>78.456.070-8</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr"/>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>1510.14</v>
+        <v>1611.68</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>3311-115-CM26</t>
+          <t>4452-534-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -21677,12 +21673,12 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -21692,28 +21688,32 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
+          <t>BROKER SPA</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>78.456.070-8</t>
-        </is>
-      </c>
-      <c r="K340" t="inlineStr"/>
+          <t>77.819.582-8</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>1611.68</v>
+        <v>1510.14</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>3385-178-CM26</t>
+          <t>4404-165-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -21733,17 +21733,17 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -21772,13 +21772,13 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>8455.41</v>
+        <v>10826.88</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>4404-165-CM26</t>
+          <t>3385-178-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -21798,17 +21798,17 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -21837,7 +21837,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>10826.88</v>
+        <v>8455.41</v>
       </c>
     </row>
     <row r="343">
@@ -21973,7 +21973,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>1029-50-CM26</t>
+          <t>967-18-CM26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -21998,12 +21998,12 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -22013,12 +22013,12 @@
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>INGENIERIA Y SEGURIDAD INDUSTRIAL KS LIMITADA</t>
+          <t>Treck S.A.</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>76.488.070-6</t>
+          <t>96.542.490-3</t>
         </is>
       </c>
       <c r="K345" t="inlineStr"/>
@@ -22028,7 +22028,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>2225.13</v>
+        <v>6769.44</v>
       </c>
     </row>
     <row r="346">
@@ -22099,7 +22099,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>967-18-CM26</t>
+          <t>1029-50-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -22124,12 +22124,12 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -22139,12 +22139,12 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>Treck S.A.</t>
+          <t>INGENIERIA Y SEGURIDAD INDUSTRIAL KS LIMITADA</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>96.542.490-3</t>
+          <t>76.488.070-6</t>
         </is>
       </c>
       <c r="K347" t="inlineStr"/>
@@ -22154,13 +22154,13 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>6769.44</v>
+        <v>2225.13</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>3876-154-CM26</t>
+          <t>3469-335-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -22185,12 +22185,12 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.120.300-k</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>I MUNICIPALIDAD DE CHANCO</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -22200,17 +22200,17 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>BROKER SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>77.819.582-8</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
@@ -22219,13 +22219,13 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>2019</v>
+        <v>5843.07</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>3469-335-CM26</t>
+          <t>3876-154-CM26</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -22250,12 +22250,12 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>69.120.300-k</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANCO</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -22265,17 +22265,17 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>BROKER SPA</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.819.582-8</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
@@ -22284,7 +22284,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>5843.07</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="350">
@@ -22355,7 +22355,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>1208066-294-CM26</t>
+          <t>3442-314-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -22375,17 +22375,17 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.100.700-6</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE VICHUQUEN</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -22395,12 +22395,12 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K351" t="inlineStr"/>
@@ -22410,13 +22410,13 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>3995.21</v>
+        <v>785.21</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>3442-314-CM26</t>
+          <t>1208066-294-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -22436,17 +22436,17 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>69.100.700-6</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICHUQUEN</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -22456,12 +22456,12 @@
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K352" t="inlineStr"/>
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>785.21</v>
+        <v>3995.21</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>4451-485-CM26</t>
+          <t>4451-483-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -22497,7 +22497,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
@@ -22517,12 +22517,12 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
@@ -22536,13 +22536,13 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>9191.559999999999</v>
+        <v>1245.7</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>4451-483-CM26</t>
+          <t>4451-484-CM26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -22562,7 +22562,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
@@ -22582,17 +22582,17 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
@@ -22601,13 +22601,13 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>1245.7</v>
+        <v>1152.25</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>4451-484-CM26</t>
+          <t>4451-485-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -22647,17 +22647,17 @@
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
@@ -22666,13 +22666,13 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>1152.25</v>
+        <v>9191.559999999999</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>1420-25-CM26</t>
+          <t>2445-2352-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -22697,12 +22697,12 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -22712,12 +22712,12 @@
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>Treck S.A.</t>
+          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>96.542.490-3</t>
+          <t>76.950.108-8</t>
         </is>
       </c>
       <c r="K356" t="inlineStr"/>
@@ -22727,13 +22727,13 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>4392.36</v>
+        <v>2638.25</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2445-2352-CM26</t>
+          <t>1420-25-CM26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -22758,12 +22758,12 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -22773,12 +22773,12 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
+          <t>Treck S.A.</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>76.950.108-8</t>
+          <t>96.542.490-3</t>
         </is>
       </c>
       <c r="K357" t="inlineStr"/>
@@ -22788,13 +22788,13 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>2638.25</v>
+        <v>4392.36</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>4314-308-CM26</t>
+          <t>4451-499-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -22814,17 +22814,17 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>69.110.300-5</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Curepto</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -22834,17 +22834,17 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA WAY SPA</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.532.399-1</t>
         </is>
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
@@ -22853,13 +22853,13 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>7559.04</v>
+        <v>7664.54</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>4451-499-CM26</t>
+          <t>4314-308-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -22879,17 +22879,17 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.110.300-5</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -22899,17 +22899,17 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA WAY SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>76.532.399-1</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
@@ -22918,13 +22918,13 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>7664.54</v>
+        <v>7559.04</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2132-257-CM26</t>
+          <t>4451-512-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -22944,17 +22944,17 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -22983,13 +22983,13 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>4424.21</v>
+        <v>2060.61</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>3287-427-CM26</t>
+          <t>4451-511-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -23014,12 +23014,12 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>69.100.500-3</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LICANTEN</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -23029,28 +23029,32 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingeniería eléctrica Ingelor Limitada  </t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>77.218.691-6</t>
-        </is>
-      </c>
-      <c r="K361" t="inlineStr"/>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>3694.45</v>
+        <v>3567.87</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>4451-511-CM26</t>
+          <t>3287-427-CM26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -23075,12 +23079,12 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.100.500-3</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -23090,32 +23094,28 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t xml:space="preserve">Ingeniería eléctrica Ingelor Limitada  </t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
-        </is>
-      </c>
-      <c r="K362" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.218.691-6</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr"/>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>3567.87</v>
+        <v>3694.45</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>4451-512-CM26</t>
+          <t>2132-257-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -23135,17 +23135,17 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -23174,7 +23174,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>2060.61</v>
+        <v>4424.21</v>
       </c>
     </row>
     <row r="364">
@@ -24050,7 +24050,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>1391-1836-CM26</t>
+          <t>2292-7128-CM26</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -24090,12 +24090,12 @@
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K378" t="inlineStr">
@@ -24109,13 +24109,13 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>830.08</v>
+        <v>3109.64</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2292-7128-CM26</t>
+          <t>1391-1836-CM26</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -24135,17 +24135,17 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -24155,12 +24155,12 @@
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K379" t="inlineStr">
@@ -24174,7 +24174,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>3109.64</v>
+        <v>830.08</v>
       </c>
     </row>
     <row r="380">
@@ -24261,7 +24261,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
@@ -24302,7 +24302,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>4314-388-CM26</t>
+          <t>1391-1589-CM26</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -24317,7 +24317,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -24327,12 +24327,12 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>69.110.300-5</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Curepto</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -24342,17 +24342,17 @@
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
@@ -24361,68 +24361,1190 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>2195.78</v>
+        <v>1494.99</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
+          <t>4314-388-CM26</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>69.110.300-5</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Curepto</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M383" s="2" t="n">
+        <v>2195.78</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
           <t>2292-7178-CM26</t>
         </is>
       </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>2239-9-LR23</t>
-        </is>
-      </c>
-      <c r="C383" t="inlineStr">
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr">
+      <c r="D384" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="E383" t="inlineStr">
+      <c r="E384" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F383" t="inlineStr">
+      <c r="F384" t="inlineStr">
         <is>
           <t>69.110.400-1</t>
         </is>
       </c>
-      <c r="G383" t="inlineStr">
+      <c r="G384" t="inlineStr">
         <is>
           <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
-      <c r="H383" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I383" t="inlineStr">
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
         <is>
           <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
-      <c r="J383" t="inlineStr">
+      <c r="J384" t="inlineStr">
         <is>
           <t>77.676.860-k</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
-      <c r="L383" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M383" s="2" t="n">
+      <c r="K384" t="inlineStr"/>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M384" s="2" t="n">
         <v>1070.91</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2292-7179-CM26</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M385" s="2" t="n">
+        <v>1048.72</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>3206-343-CM26</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>69.264.500-6</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>INGENIERIA Y SEGURIDAD INDUSTRIAL KS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>76.488.070-6</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr"/>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M386" s="2" t="n">
+        <v>1549.53</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>4451-629-CM26</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>69.110.500-8</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>76.950.108-8</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr"/>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M387" s="2" t="n">
+        <v>22450.35</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2294-2136-CM26</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr"/>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M388" s="2" t="n">
+        <v>805.6</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>1420-32-CM26</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>Treck S.A.</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>96.542.490-3</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr"/>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M389" s="2" t="n">
+        <v>3254.4</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>3756-707-CM26</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>69.110.600-4</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr"/>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M390" s="2" t="n">
+        <v>6246.74</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>1090-106-CM26</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Treck S.A.</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>96.542.490-3</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr"/>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M391" s="2" t="n">
+        <v>3278.02</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2291-1629-CM26</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>76.099.725-0</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr"/>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M392" s="2" t="n">
+        <v>14734.64</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>1495207-14-CM26</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>COMERCIAL TREBOL LIMITADA</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>77.601.801-5</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M393" s="2" t="n">
+        <v>824.6900000000001</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2291-1632-CM26</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>76.099.725-0</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr"/>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M394" s="2" t="n">
+        <v>5911.06</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>4451-666-CM26</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>69.110.500-8</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr"/>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M395" s="2" t="n">
+        <v>4405.69</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>848-238-CM26</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr"/>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M396" s="2" t="n">
+        <v>1465.15</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2291-1643-CM26</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M397" s="2" t="n">
+        <v>4760.93</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>1982-18-CM26</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>Treck S.A.</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>96.542.490-3</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr"/>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M398" s="2" t="n">
+        <v>4199.02</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2291-1655-CM26</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M399" s="2" t="n">
+        <v>1028.47</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>955-22-CM26</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>Treck S.A.</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>96.542.490-3</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr"/>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M400" s="2" t="n">
+        <v>3214.71</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2436-1430-CM26</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>69.100.100-8</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CURICO</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>TECNOQUIM SPA</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>76.378.846-6</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M401" s="2" t="n">
+        <v>6528.83</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/maule.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/maule.xlsx
@@ -24891,7 +24891,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
